--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T19:47:50+00:00</t>
+    <t>2026-02-22T11:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the overall Questionnaire for PreNUDGE.</t>
+    <t>This FHIR profile is defining the overall Questionnaire for PreNUDGE. Every top level item requires one comment subitem, with the linkId ending or equal 'comment'.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -979,7 +979,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}</t>
+que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}at-prenudge-every-item-has-comment:Jedes top-level Item muss genau ein Unter-Item enthalten, dessen linkId auf 'comment' endet {item.where(linkId.endsWith('comment') and type = 'string').count() = 1}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=OBS, moodCode=DEF]</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T07:03:20+00:00</t>
+    <t>2026-02-26T10:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:01:13+00:00</t>
+    <t>2026-02-28T09:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -979,7 +979,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}at-prenudge-every-item-has-comment:Jedes top-level Item muss genau ein Unter-Item enthalten, dessen linkId auf 'comment' endet {item.where(linkId.endsWith('comment') and type = 'string').count() = 1}</t>
+que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}at-prenudge-every-item-has-comment:Jedes top-level Item muss genau ein Unter-Item enthalten, dessen linkId auf 'comment' endet {type = 'display' or item.where(linkId.endsWith('comment') and type = 'string').count() = 1}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=OBS, moodCode=DEF]</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the overall Questionnaire for PreNUDGE. Every top level item requires one comment subitem, with the linkId ending or equal 'comment'.</t>
+    <t>This FHIR profile is defining the overall Questionnaire for PreNUDGE. Every top level item requires one comment subitem, with the linkId ending or equal 'comment'. Be aware that if the user enters values from a device into a questionnaire, it is still considered a manual input. Please keep in mind that all questionnaires must comply with the qualification matrix on https://prenudge.at/qualificationmatrix/.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -979,7 +979,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}at-prenudge-every-item-has-comment:Jedes top-level Item muss genau ein Unter-Item enthalten, dessen linkId auf 'comment' endet {type = 'display' or item.where(linkId.endsWith('comment') and type = 'string').count() = 1}</t>
+que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}at-prenudge-every-item-has-comment:Jedes top-level Item muss genau ein Unter-Item enthalten, dessen linkId auf 'comment' endet {type = 'display' or item.where(linkId.endsWith('comment') and type = 'string').count() &gt;= 1}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=OBS, moodCode=DEF]</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
